--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-019_通知一覧取得_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-019_通知一覧取得_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="7600950"/>
+    <ext cx="8572500" cy="7810500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-019 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-019 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="169" customHeight="1">
+    <row r="3" ht="214" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -2471,7 +2471,8 @@
       <c r="D3" s="7" t="inlineStr">
         <is>
           <t>・確定設計変更 D1〜D10 を反映：応答に type / requestId を追加し画面は requestId があれば SCR-106 へ遷移（旧『SCR-106 で代替』を廃止）、notify の保存内容を type / request_id 込みに更新、existsMonthly を追加、既読化の updated_at をトリガ自動更新に変更（now / Clock を削除）、数値でない id を 400 / E-002 に、トークン不正を 401 / E-001 の JSON に更新
-・BAT-002 との食い違い解消：NotificationService#existsMonthly(Long userId, String type, String keyPrefix, YearMonth yearMonth) の 4 引数 overload（本文前方一致）と NotificationRepository#existsByUserIdAndTypeAndMessageStartingWith…（疑似コード・SQL・テスト）を追加。3 引数版は残す</t>
+・BAT-002 との食い違い解消：NotificationService#existsMonthly(Long userId, String type, String keyPrefix, YearMonth yearMonth) の 4 引数 overload（本文前方一致）と NotificationRepository#existsByUserIdAndTypeAndMessageStartingWith…（疑似コード・SQL・テスト）を追加。3 引数版は残す
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3972,7 +3973,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Controller: Long.valueOf(jwt.getSubject())。他人の userId は受け取らない</t>
+          <t>Controller: Long.valueOf(auth.getName())。他人の userId は受け取らない</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -4137,7 +4138,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public NotificationListResponse list(@AuthenticationPrincipal Jwt jwt)</t>
+          <t>public NotificationListResponse list(Authentication auth)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -4201,17 +4202,17 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン。sub = users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -4258,7 +4259,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>1. Long userId = Long.valueOf(jwt.getSubject());
+          <t>1. Long userId = Long.valueOf(auth.getName());
 2. return notificationService.getNotifications(userId);</t>
         </is>
       </c>
@@ -4337,7 +4338,7 @@
         <is>
           <t>public NotificationResponse markAsRead(
     @PathVariable("id") Long id,
-    @AuthenticationPrincipal Jwt jwt)</t>
+    Authentication auth)</t>
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
@@ -4420,17 +4421,17 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン。sub = users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
@@ -4478,7 +4479,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>1. Long userId = Long.valueOf(jwt.getSubject());
+          <t>1. Long userId = Long.valueOf(auth.getName());
 2. return notificationService.markAsRead(userId, id);</t>
         </is>
       </c>
@@ -6903,7 +6904,7 @@
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>Controller: Long.valueOf(jwt.getSubject())</t>
+          <t>Controller: Long.valueOf(auth.getName())</t>
         </is>
       </c>
       <c r="D177" s="9" t="n"/>
